--- a/data/pack/uk/huevos_campero_uk.xlsx
+++ b/data/pack/uk/huevos_campero_uk.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6759,6 +6759,61 @@
         </is>
       </c>
       <c r="K115" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: Defra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>huevos_campero_uk</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Huevos camperos, precio al productor (Reino Unido)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>docena</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>UK Defra (gov.uk agricultural statistics)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: Defra.</t>
         </is>
@@ -6862,7 +6917,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6928,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
@@ -6968,7 +7023,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
